--- a/AAII_Financials/Yearly/JHX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JHX_YR_FIN.xlsx
@@ -2972,10 +2972,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>87900</v>
+        <v>82300</v>
       </c>
       <c r="E58" s="3">
-        <v>33200</v>
+        <v>32100</v>
       </c>
       <c r="F58" s="3">
         <v>27700</v>
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>286400</v>
+        <v>292000</v>
       </c>
       <c r="E59" s="3">
-        <v>269200</v>
+        <v>270300</v>
       </c>
       <c r="F59" s="3">
         <v>237300</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4801300</v>
+        <v>4703400</v>
       </c>
       <c r="E61" s="3">
-        <v>1177800</v>
+        <v>1175900</v>
       </c>
       <c r="F61" s="3">
         <v>1176600</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>904700</v>
+        <v>1002600</v>
       </c>
       <c r="E62" s="3">
-        <v>959300</v>
+        <v>961200</v>
       </c>
       <c r="F62" s="3">
         <v>971900</v>
